--- a/data/BACTERIA_data/BACTERIADATA.xlsx
+++ b/data/BACTERIA_data/BACTERIADATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB_REPO\eoanalysis\scripts\data\BACTERIA_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GITHUB_REPO\biogps_essoils\data\BACTERIA_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A11BED-B32B-473C-966A-91455ED3B956}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C78465-301A-40BD-ACBF-BD420CDB5C83}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8652" xr2:uid="{EDD9F0D8-A8AD-443C-BCBA-14F316F73C1D}"/>
   </bookViews>
@@ -595,7 +595,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,8 +604,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -631,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -640,8 +647,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -967,19 +978,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>156</v>
       </c>
     </row>
@@ -1222,7 +1233,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1533,10 +1544,10 @@
       <c r="A35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>137</v>
       </c>
       <c r="D35" s="1">
